--- a/evac_by_zip/evac_by_zip_2026-09-16.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-09-16.xlsx
@@ -63,7 +63,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002C3E50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -129,15 +124,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -170,12 +156,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -546,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -569,7 +549,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 169 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 144 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -625,45 +605,43 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>29</v>
-      </c>
       <c r="E4" s="4" t="n">
-        <v>29</v>
+        <v>231</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>97023</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -671,64 +649,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>225</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>231</v>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
@@ -737,96 +679,64 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
+          <t>Placed on a ZIP code (table above)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="E7" s="8" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Not placed on any ZIP code (unmatched)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
+      <c r="E8" s="10" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Placed on a ZIP code (table above)</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>225</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Not placed on any ZIP code (unmatched)</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>137</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Reconciled total (matches morning report)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B9" s="12" t="n">
         <v>362</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C9" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="D11" s="15" t="n">
-        <v>55</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>433</v>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -844,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -857,506 +767,366 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Evac Zone × ZIP Code Detail — 2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>ZIP Code</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Zone Name</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Fire Name</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
         <is>
           <t>Evac Level</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>% of Zone</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="14" t="inlineStr">
         <is>
           <t>Est. Addresses</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>29</v>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="G4" s="18" t="n">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Mill Creek Buttes</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Cooper Spur North</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Cooper Spur South</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Gibson Prairie</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>97063</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G10" s="15" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>97358</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>97028</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>White River</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G11" s="17" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>Elk Mountain</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>Cooper Spur North</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>Cooper Spur South</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Gibson Prairie</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>97021</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>97063</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -1364,8 +1134,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
